--- a/Templates/03-evaluation/business-case-tco-roi.xlsx
+++ b/Templates/03-evaluation/business-case-tco-roi.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OnPrem-StatusQuo" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year1-DualRunning" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partner-Credits" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Validation" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -30,7 +31,7 @@
     <numFmt numFmtId="167" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="168" formatCode="#,##0.0;\(#,##0.0\);\-"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -271,8 +272,42 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00E31C3D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="65">
+  <fills count="73">
     <fill>
       <patternFill/>
     </fill>
@@ -650,8 +685,48 @@
         <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9900"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004285F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="36">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1099,11 +1174,69 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="306">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1745,6 +1878,62 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="64" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="65" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="67" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="65" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="59" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="61" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="68" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="68" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="68" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="69" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="68" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="68" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="66" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="70" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="71" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="60" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="66" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="72" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2241,6 +2430,1599 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="21" min="1" max="1"/>
+    <col width="10" customWidth="1" style="21" min="2" max="2"/>
+    <col width="10" customWidth="1" style="21" min="3" max="3"/>
+    <col width="10" customWidth="1" style="21" min="4" max="4"/>
+    <col width="10" customWidth="1" style="21" min="5" max="5"/>
+    <col width="14" customWidth="1" style="21" min="6" max="6"/>
+    <col width="14" customWidth="1" style="21" min="7" max="7"/>
+    <col width="14" customWidth="1" style="21" min="8" max="8"/>
+    <col width="35" customWidth="1" style="21" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="286" t="inlineStr">
+        <is>
+          <t>4B.9 Pricing Validation -- Reference Prices for TCO Model SKUs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1" s="21">
+      <c r="A2" s="287" t="inlineStr">
+        <is>
+          <t>Purpose: Validate that the TCO model pricing assumptions are within acceptable range of current published prices. Update this tab whenever you re-use the TCO model. Prices shown are reference values; always confirm with the official pricing calculator before customer submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="21">
+      <c r="A3" s="288" t="inlineStr">
+        <is>
+          <t>IMPORTANT: Reference prices below are calibrated to June 2026 published list prices (USD). Prices vary by region; UK South / eu-west-1 / europe-west2 are typically 10-15% higher than US East. Spot/preemptible prices are not used in CRA TCO models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" s="21">
+      <c r="A4" s="289" t="inlineStr">
+        <is>
+          <t>SKU / Instance Type</t>
+        </is>
+      </c>
+      <c r="B4" s="289" t="inlineStr">
+        <is>
+          <t>vCPU</t>
+        </is>
+      </c>
+      <c r="C4" s="289" t="inlineStr">
+        <is>
+          <t>RAM (GB)</t>
+        </is>
+      </c>
+      <c r="D4" s="289" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="E4" s="289" t="inlineStr">
+        <is>
+          <t>On-Demand $/hr</t>
+        </is>
+      </c>
+      <c r="F4" s="289" t="inlineStr">
+        <is>
+          <t>3yr RI/CUD $/hr</t>
+        </is>
+      </c>
+      <c r="G4" s="289" t="inlineStr">
+        <is>
+          <t>3yr Saving %</t>
+        </is>
+      </c>
+      <c r="H4" s="289" t="inlineStr">
+        <is>
+          <t>Region Basis</t>
+        </is>
+      </c>
+      <c r="I4" s="289" t="inlineStr">
+        <is>
+          <t>Notes / Validation Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="290" t="inlineStr">
+        <is>
+          <t>MICROSOFT AZURE -- Key SKUs for CRA TCO Model</t>
+        </is>
+      </c>
+      <c r="B5" s="291" t="n"/>
+      <c r="C5" s="291" t="n"/>
+      <c r="D5" s="291" t="n"/>
+      <c r="E5" s="291" t="n"/>
+      <c r="F5" s="291" t="n"/>
+      <c r="G5" s="291" t="n"/>
+      <c r="H5" s="291" t="n"/>
+      <c r="I5" s="292" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="293" t="inlineStr">
+        <is>
+          <t>D4s_v5</t>
+        </is>
+      </c>
+      <c r="B6" s="294" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E6" s="296" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="F6" s="294" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G6" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H6" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I6" s="299" t="inlineStr">
+        <is>
+          <t>General purpose. Standard migration target for &lt;32GB RAM workloads. AHB reduces Windows cost by ~40%. Source: azure.microsoft.com/pricing/details/virtual-machines/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="293" t="inlineStr">
+        <is>
+          <t>D8s_v5</t>
+        </is>
+      </c>
+      <c r="B7" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D7" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E7" s="296" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F7" s="294" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="G7" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H7" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I7" s="299" t="inlineStr">
+        <is>
+          <t>Most common migration target (matches m6i.2xlarge). Dsv5 = Dav5 replacement; better perf/price than Dsv4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="293" t="inlineStr">
+        <is>
+          <t>D16s_v5</t>
+        </is>
+      </c>
+      <c r="B8" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="294" t="n">
+        <v>64</v>
+      </c>
+      <c r="D8" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E8" s="296" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="F8" s="294" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="G8" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H8" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I8" s="299" t="inlineStr">
+        <is>
+          <t>Large general workloads. Check if E-series more cost-effective for memory-heavy workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="293" t="inlineStr">
+        <is>
+          <t>E4s_v5</t>
+        </is>
+      </c>
+      <c r="B9" s="294" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E9" s="296" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="F9" s="294" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="G9" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H9" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I9" s="299" t="inlineStr">
+        <is>
+          <t>Memory-optimised. Use for SQL Server, Redis, in-memory cache workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="293" t="inlineStr">
+        <is>
+          <t>E8s_v5</t>
+        </is>
+      </c>
+      <c r="B10" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="294" t="n">
+        <v>64</v>
+      </c>
+      <c r="D10" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E10" s="296" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="F10" s="294" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G10" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H10" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I10" s="299" t="inlineStr">
+        <is>
+          <t>SQL Server primary target. AHB on SQL Server = up to 55% cost reduction. Key SKU for CRA engagements with large SQL Server estates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="293" t="inlineStr">
+        <is>
+          <t>E16s_v5</t>
+        </is>
+      </c>
+      <c r="B11" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C11" s="294" t="n">
+        <v>128</v>
+      </c>
+      <c r="D11" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E11" s="296" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="F11" s="294" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G11" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H11" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I11" s="299" t="inlineStr">
+        <is>
+          <t>High-memory workloads. Check Oracle BYOL eligibility before recommending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="293" t="inlineStr">
+        <is>
+          <t>M8ms</t>
+        </is>
+      </c>
+      <c r="B12" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="294" t="n">
+        <v>218</v>
+      </c>
+      <c r="D12" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E12" s="296" t="n">
+        <v>1.872</v>
+      </c>
+      <c r="F12" s="294" t="n">
+        <v>1.151</v>
+      </c>
+      <c r="G12" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H12" s="298" t="inlineStr">
+        <is>
+          <t>East US</t>
+        </is>
+      </c>
+      <c r="I12" s="299" t="inlineStr">
+        <is>
+          <t>SAP HANA and large Oracle workloads. Premium pricing tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="293" t="inlineStr">
+        <is>
+          <t>D8s_v5</t>
+        </is>
+      </c>
+      <c r="B13" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D13" s="295" t="inlineStr">
+        <is>
+          <t>Temp SSD</t>
+        </is>
+      </c>
+      <c r="E13" s="296" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F13" s="294" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="G13" s="297" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="H13" s="298" t="inlineStr">
+        <is>
+          <t>UK South (+12.5%)</t>
+        </is>
+      </c>
+      <c r="I13" s="299" t="inlineStr">
+        <is>
+          <t>UK South add-on: ~12.5% premium over East US. Use this for UK-based CRA engagements (e.g., DMG Media UK).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="300" t="inlineStr">
+        <is>
+          <t>Azure Hybrid Benefit (AHB): Windows Server AHB saves ~40% on OS component. SQL Server AHB saves up to 55% (Standard licence). Apply AHB savings separately in the Licensing-Overlay tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="301" t="inlineStr">
+        <is>
+          <t>AWS -- Key SKUs for CRA TCO Model</t>
+        </is>
+      </c>
+      <c r="B15" s="291" t="n"/>
+      <c r="C15" s="291" t="n"/>
+      <c r="D15" s="291" t="n"/>
+      <c r="E15" s="291" t="n"/>
+      <c r="F15" s="291" t="n"/>
+      <c r="G15" s="291" t="n"/>
+      <c r="H15" s="291" t="n"/>
+      <c r="I15" s="292" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="293" t="inlineStr">
+        <is>
+          <t>m6i.xlarge</t>
+        </is>
+      </c>
+      <c r="B16" s="294" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E16" s="296" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="F16" s="294" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="G16" s="297" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="H16" s="298" t="inlineStr">
+        <is>
+          <t>us-east-1</t>
+        </is>
+      </c>
+      <c r="I16" s="299" t="inlineStr">
+        <is>
+          <t>General purpose. Current-gen Intel-based. Source: aws.amazon.com/ec2/pricing/reserved-instances/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="293" t="inlineStr">
+        <is>
+          <t>m6i.2xlarge</t>
+        </is>
+      </c>
+      <c r="B17" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E17" s="296" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F17" s="294" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="G17" s="297" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="H17" s="298" t="inlineStr">
+        <is>
+          <t>us-east-1</t>
+        </is>
+      </c>
+      <c r="I17" s="299" t="inlineStr">
+        <is>
+          <t>Most common migration target. 3yr All-Upfront RI pricing shown. Savings Plans can match or beat RI pricing with more flexibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="293" t="inlineStr">
+        <is>
+          <t>m6i.4xlarge</t>
+        </is>
+      </c>
+      <c r="B18" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="294" t="n">
+        <v>64</v>
+      </c>
+      <c r="D18" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E18" s="296" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="F18" s="294" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G18" s="297" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="H18" s="298" t="inlineStr">
+        <is>
+          <t>us-east-1</t>
+        </is>
+      </c>
+      <c r="I18" s="299" t="inlineStr">
+        <is>
+          <t>Large general workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="293" t="inlineStr">
+        <is>
+          <t>r6i.2xlarge</t>
+        </is>
+      </c>
+      <c r="B19" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" s="294" t="n">
+        <v>64</v>
+      </c>
+      <c r="D19" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E19" s="296" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="F19" s="294" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="G19" s="297" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="H19" s="298" t="inlineStr">
+        <is>
+          <t>us-east-1</t>
+        </is>
+      </c>
+      <c r="I19" s="299" t="inlineStr">
+        <is>
+          <t>Memory-optimised. RDS/MySQL/Oracle workloads. r6i replaces r5; 15% better perf/price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="293" t="inlineStr">
+        <is>
+          <t>r6i.4xlarge</t>
+        </is>
+      </c>
+      <c r="B20" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" s="294" t="n">
+        <v>128</v>
+      </c>
+      <c r="D20" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E20" s="296" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="F20" s="294" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="G20" s="297" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="H20" s="298" t="inlineStr">
+        <is>
+          <t>us-east-1</t>
+        </is>
+      </c>
+      <c r="I20" s="299" t="inlineStr">
+        <is>
+          <t>Large memory workloads. Compare vs Azure E16s_v5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="293" t="inlineStr">
+        <is>
+          <t>m6i.2xlarge</t>
+        </is>
+      </c>
+      <c r="B21" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C21" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D21" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E21" s="296" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="F21" s="294" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="G21" s="297" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="H21" s="298" t="inlineStr">
+        <is>
+          <t>eu-west-2 (London)</t>
+        </is>
+      </c>
+      <c r="I21" s="299" t="inlineStr">
+        <is>
+          <t>London region add-on: ~12.5% premium over us-east-1. Use for UK-based CRA engagements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="293" t="inlineStr">
+        <is>
+          <t>m7i.2xlarge</t>
+        </is>
+      </c>
+      <c r="B22" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D22" s="295" t="inlineStr">
+        <is>
+          <t>EBS only</t>
+        </is>
+      </c>
+      <c r="E22" s="296" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="F22" s="294" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="G22" s="297" t="inlineStr">
+        <is>
+          <t>38.7%</t>
+        </is>
+      </c>
+      <c r="H22" s="298" t="inlineStr">
+        <is>
+          <t>us-east-1</t>
+        </is>
+      </c>
+      <c r="I22" s="299" t="inlineStr">
+        <is>
+          <t>Latest gen (Sapphire Rapids). 15% better perf/price vs m6i. Use as default for new deployment recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="300" t="inlineStr">
+        <is>
+          <t>AWS Savings Plans (Compute) typically match 3yr RI All-Upfront savings while offering more flexibility (apply across instance families and regions). Use Savings Plans pricing in TCO model unless customer has existing RI portfolio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="302" t="inlineStr">
+        <is>
+          <t>GOOGLE CLOUD PLATFORM -- Key SKUs for CRA TCO Model</t>
+        </is>
+      </c>
+      <c r="B24" s="291" t="n"/>
+      <c r="C24" s="291" t="n"/>
+      <c r="D24" s="291" t="n"/>
+      <c r="E24" s="291" t="n"/>
+      <c r="F24" s="291" t="n"/>
+      <c r="G24" s="291" t="n"/>
+      <c r="H24" s="291" t="n"/>
+      <c r="I24" s="292" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="293" t="inlineStr">
+        <is>
+          <t>n2-standard-4</t>
+        </is>
+      </c>
+      <c r="B25" s="294" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E25" s="296" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F25" s="294" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="G25" s="297" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="H25" s="298" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="I25" s="299" t="inlineStr">
+        <is>
+          <t>General purpose. CUD discount is deeper than Azure RI/AWS RI at ~50%. Source: cloud.google.com/compute/vm-instance-pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="293" t="inlineStr">
+        <is>
+          <t>n2-standard-8</t>
+        </is>
+      </c>
+      <c r="B26" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E26" s="296" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="F26" s="294" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G26" s="297" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="H26" s="298" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="I26" s="299" t="inlineStr">
+        <is>
+          <t>Most common CRA migration target. 3yr CUD pricing shown. Sustained Use Discounts (SUDs) apply automatically for &gt;25% month usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="293" t="inlineStr">
+        <is>
+          <t>n2-standard-16</t>
+        </is>
+      </c>
+      <c r="B27" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" s="294" t="n">
+        <v>64</v>
+      </c>
+      <c r="D27" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E27" s="296" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="F27" s="294" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="G27" s="297" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="H27" s="298" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="I27" s="299" t="inlineStr">
+        <is>
+          <t>Large general workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="293" t="inlineStr">
+        <is>
+          <t>n2-highmem-4</t>
+        </is>
+      </c>
+      <c r="B28" s="294" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D28" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E28" s="296" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="F28" s="294" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G28" s="297" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="H28" s="298" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="I28" s="299" t="inlineStr">
+        <is>
+          <t>Memory-optimised (8GB/vCPU ratio). Use for SQL, SAP workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="293" t="inlineStr">
+        <is>
+          <t>n2-highmem-8</t>
+        </is>
+      </c>
+      <c r="B29" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="294" t="n">
+        <v>64</v>
+      </c>
+      <c r="D29" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E29" s="296" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="F29" s="294" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="G29" s="297" t="inlineStr">
+        <is>
+          <t>49.5%</t>
+        </is>
+      </c>
+      <c r="H29" s="298" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="I29" s="299" t="inlineStr">
+        <is>
+          <t>Primary CRA memory-optimised target. Compare vs Azure E8s_v5 and AWS r6i.2xlarge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="293" t="inlineStr">
+        <is>
+          <t>n2-highmem-16</t>
+        </is>
+      </c>
+      <c r="B30" s="294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C30" s="294" t="n">
+        <v>128</v>
+      </c>
+      <c r="D30" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E30" s="296" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="F30" s="294" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="G30" s="297" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="H30" s="298" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="I30" s="299" t="inlineStr">
+        <is>
+          <t>Large memory workloads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="293" t="inlineStr">
+        <is>
+          <t>n2-standard-8</t>
+        </is>
+      </c>
+      <c r="B31" s="294" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="294" t="n">
+        <v>32</v>
+      </c>
+      <c r="D31" s="295" t="inlineStr">
+        <is>
+          <t>Persistent</t>
+        </is>
+      </c>
+      <c r="E31" s="296" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="F31" s="294" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="G31" s="297" t="inlineStr">
+        <is>
+          <t>49.4%</t>
+        </is>
+      </c>
+      <c r="H31" s="298" t="inlineStr">
+        <is>
+          <t>europe-west2 (London)</t>
+        </is>
+      </c>
+      <c r="I31" s="299" t="inlineStr">
+        <is>
+          <t>London region add-on: ~15% premium over us-east1. Use for UK-based CRA engagements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="300" t="inlineStr">
+        <is>
+          <t>GCP Committed Use Discounts (CUD): 3yr resource-based CUD gives ~50% discount on CPU/RAM. GCP Sustained Use Discounts (SUD) apply automatically at up to 30% for full-month usage. CUDs stack with SUDs on the non-CUD portion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="303" t="inlineStr">
+        <is>
+          <t>VALIDATION CHECKLIST -- Complete before customer TCO submission</t>
+        </is>
+      </c>
+      <c r="B33" s="291" t="n"/>
+      <c r="C33" s="291" t="n"/>
+      <c r="D33" s="291" t="n"/>
+      <c r="E33" s="291" t="n"/>
+      <c r="F33" s="291" t="n"/>
+      <c r="G33" s="291" t="n"/>
+      <c r="H33" s="291" t="n"/>
+      <c r="I33" s="292" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="289" t="inlineStr">
+        <is>
+          <t>Validation Check</t>
+        </is>
+      </c>
+      <c r="B34" s="289" t="inlineStr">
+        <is>
+          <t>Source / Tab</t>
+        </is>
+      </c>
+      <c r="C34" s="289" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="D34" s="291" t="n"/>
+      <c r="E34" s="291" t="n"/>
+      <c r="F34" s="291" t="n"/>
+      <c r="G34" s="291" t="n"/>
+      <c r="H34" s="292" t="n"/>
+      <c r="I34" s="289" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" s="21">
+      <c r="A35" s="293" t="inlineStr">
+        <is>
+          <t>Azure pricing validated</t>
+        </is>
+      </c>
+      <c r="B35" s="299" t="inlineStr">
+        <is>
+          <t>azure.microsoft.com/pricing/calculator</t>
+        </is>
+      </c>
+      <c r="C35" s="298" t="inlineStr">
+        <is>
+          <t>Confirm Dsv5 and Esv5 pricing in target region and commitment tier</t>
+        </is>
+      </c>
+      <c r="D35" s="291" t="n"/>
+      <c r="E35" s="291" t="n"/>
+      <c r="F35" s="291" t="n"/>
+      <c r="G35" s="291" t="n"/>
+      <c r="H35" s="292" t="n"/>
+      <c r="I35" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" s="21">
+      <c r="A36" s="293" t="inlineStr">
+        <is>
+          <t>Azure AHB saving calculated</t>
+        </is>
+      </c>
+      <c r="B36" s="299" t="inlineStr">
+        <is>
+          <t>LICENSING-OVERLAY tab</t>
+        </is>
+      </c>
+      <c r="C36" s="298" t="inlineStr">
+        <is>
+          <t>Apply AHB to all AHB-eligible VMs (Windows + SQL). Record count and saving.</t>
+        </is>
+      </c>
+      <c r="D36" s="291" t="n"/>
+      <c r="E36" s="291" t="n"/>
+      <c r="F36" s="291" t="n"/>
+      <c r="G36" s="291" t="n"/>
+      <c r="H36" s="292" t="n"/>
+      <c r="I36" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" s="21">
+      <c r="A37" s="293" t="inlineStr">
+        <is>
+          <t>Azure ESU saving calculated</t>
+        </is>
+      </c>
+      <c r="B37" s="299" t="inlineStr">
+        <is>
+          <t>LICENSING-OVERLAY tab</t>
+        </is>
+      </c>
+      <c r="C37" s="298" t="inlineStr">
+        <is>
+          <t>Identify EoL OS count. Azure ESU is included free -- model as on-prem ESU cost avoided.</t>
+        </is>
+      </c>
+      <c r="D37" s="291" t="n"/>
+      <c r="E37" s="291" t="n"/>
+      <c r="F37" s="291" t="n"/>
+      <c r="G37" s="291" t="n"/>
+      <c r="H37" s="292" t="n"/>
+      <c r="I37" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" s="21">
+      <c r="A38" s="293" t="inlineStr">
+        <is>
+          <t>AWS pricing validated</t>
+        </is>
+      </c>
+      <c r="B38" s="299" t="inlineStr">
+        <is>
+          <t>aws.amazon.com/ec2/pricing</t>
+        </is>
+      </c>
+      <c r="C38" s="298" t="inlineStr">
+        <is>
+          <t>Confirm m6i/r6i (or m7i for new deployments) in target region and RI/Savings Plan tier</t>
+        </is>
+      </c>
+      <c r="D38" s="291" t="n"/>
+      <c r="E38" s="291" t="n"/>
+      <c r="F38" s="291" t="n"/>
+      <c r="G38" s="291" t="n"/>
+      <c r="H38" s="292" t="n"/>
+      <c r="I38" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" s="21">
+      <c r="A39" s="293" t="inlineStr">
+        <is>
+          <t>AWS MAP credit estimated</t>
+        </is>
+      </c>
+      <c r="B39" s="299" t="inlineStr">
+        <is>
+          <t>PARTNER-CREDITS tab</t>
+        </is>
+      </c>
+      <c r="C39" s="298" t="inlineStr">
+        <is>
+          <t>MAP credit estimate: typically 20-25% of migration services cost. Confirm with AWS team.</t>
+        </is>
+      </c>
+      <c r="D39" s="291" t="n"/>
+      <c r="E39" s="291" t="n"/>
+      <c r="F39" s="291" t="n"/>
+      <c r="G39" s="291" t="n"/>
+      <c r="H39" s="292" t="n"/>
+      <c r="I39" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="21">
+      <c r="A40" s="293" t="inlineStr">
+        <is>
+          <t>GCP pricing validated</t>
+        </is>
+      </c>
+      <c r="B40" s="299" t="inlineStr">
+        <is>
+          <t>cloud.google.com/compute/vm-instance-pricing</t>
+        </is>
+      </c>
+      <c r="C40" s="298" t="inlineStr">
+        <is>
+          <t>Confirm n2-standard / n2-highmem in target region and 3yr CUD tier</t>
+        </is>
+      </c>
+      <c r="D40" s="291" t="n"/>
+      <c r="E40" s="291" t="n"/>
+      <c r="F40" s="291" t="n"/>
+      <c r="G40" s="291" t="n"/>
+      <c r="H40" s="292" t="n"/>
+      <c r="I40" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" s="21">
+      <c r="A41" s="293" t="inlineStr">
+        <is>
+          <t>GCP PSO credit estimated</t>
+        </is>
+      </c>
+      <c r="B41" s="299" t="inlineStr">
+        <is>
+          <t>PARTNER-CREDITS tab</t>
+        </is>
+      </c>
+      <c r="C41" s="298" t="inlineStr">
+        <is>
+          <t>PSO credits: typically $10K-$150K depending on workload size. Confirm with GCP team.</t>
+        </is>
+      </c>
+      <c r="D41" s="291" t="n"/>
+      <c r="E41" s="291" t="n"/>
+      <c r="F41" s="291" t="n"/>
+      <c r="G41" s="291" t="n"/>
+      <c r="H41" s="292" t="n"/>
+      <c r="I41" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" s="21">
+      <c r="A42" s="293" t="inlineStr">
+        <is>
+          <t>On-prem baseline validated</t>
+        </is>
+      </c>
+      <c r="B42" s="299" t="inlineStr">
+        <is>
+          <t>ONPREM-STATUSQUO tab</t>
+        </is>
+      </c>
+      <c r="C42" s="298" t="inlineStr">
+        <is>
+          <t>Ensure hardware refresh cost, VMware licensing, DC facilities, and ESU are all included.</t>
+        </is>
+      </c>
+      <c r="D42" s="291" t="n"/>
+      <c r="E42" s="291" t="n"/>
+      <c r="F42" s="291" t="n"/>
+      <c r="G42" s="291" t="n"/>
+      <c r="H42" s="292" t="n"/>
+      <c r="I42" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1" s="21">
+      <c r="A43" s="293" t="inlineStr">
+        <is>
+          <t>Year 1 dual-running modelled</t>
+        </is>
+      </c>
+      <c r="B43" s="299" t="inlineStr">
+        <is>
+          <t>YEAR1-DUALRUNNING tab</t>
+        </is>
+      </c>
+      <c r="C43" s="298" t="inlineStr">
+        <is>
+          <t>Year 1 includes: on-prem remaining + cloud ramp-up + migration tooling + PS cost.</t>
+        </is>
+      </c>
+      <c r="D43" s="291" t="n"/>
+      <c r="E43" s="291" t="n"/>
+      <c r="F43" s="291" t="n"/>
+      <c r="G43" s="291" t="n"/>
+      <c r="H43" s="292" t="n"/>
+      <c r="I43" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" s="21">
+      <c r="A44" s="293" t="inlineStr">
+        <is>
+          <t>Regional pricing applied</t>
+        </is>
+      </c>
+      <c r="B44" s="299" t="inlineStr">
+        <is>
+          <t>ALL CLOUD TABS</t>
+        </is>
+      </c>
+      <c r="C44" s="298" t="inlineStr">
+        <is>
+          <t>Confirm UK/EU regional pricing premiums applied (Azure UK South +12.5%, AWS eu-west-2 +12.5%, GCP europe-west2 +15% vs US East baseline).</t>
+        </is>
+      </c>
+      <c r="D44" s="291" t="n"/>
+      <c r="E44" s="291" t="n"/>
+      <c r="F44" s="291" t="n"/>
+      <c r="G44" s="291" t="n"/>
+      <c r="H44" s="292" t="n"/>
+      <c r="I44" s="304" t="inlineStr">
+        <is>
+          <t>[ ] Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="305" t="inlineStr">
+        <is>
+          <t>OFFICIAL PRICING SOURCES</t>
+        </is>
+      </c>
+      <c r="B45" s="291" t="n"/>
+      <c r="C45" s="291" t="n"/>
+      <c r="D45" s="291" t="n"/>
+      <c r="E45" s="291" t="n"/>
+      <c r="F45" s="291" t="n"/>
+      <c r="G45" s="291" t="n"/>
+      <c r="H45" s="291" t="n"/>
+      <c r="I45" s="292" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="293" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="B46" s="298" t="inlineStr">
+        <is>
+          <t>https://azure.microsoft.com/pricing/details/virtual-machines/</t>
+        </is>
+      </c>
+      <c r="C46" s="291" t="n"/>
+      <c r="D46" s="291" t="n"/>
+      <c r="E46" s="291" t="n"/>
+      <c r="F46" s="291" t="n"/>
+      <c r="G46" s="292" t="n"/>
+      <c r="H46" s="299" t="inlineStr">
+        <is>
+          <t>Azure VM pricing by region and commitment tier</t>
+        </is>
+      </c>
+      <c r="I46" s="292" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="293" t="inlineStr">
+        <is>
+          <t>Azure Calculator</t>
+        </is>
+      </c>
+      <c r="B47" s="298" t="inlineStr">
+        <is>
+          <t>https://azure.microsoft.com/pricing/calculator/</t>
+        </is>
+      </c>
+      <c r="C47" s="291" t="n"/>
+      <c r="D47" s="291" t="n"/>
+      <c r="E47" s="291" t="n"/>
+      <c r="F47" s="291" t="n"/>
+      <c r="G47" s="292" t="n"/>
+      <c r="H47" s="299" t="inlineStr">
+        <is>
+          <t>Build a configurable estimate; export for TCO model validation</t>
+        </is>
+      </c>
+      <c r="I47" s="292" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="293" t="inlineStr">
+        <is>
+          <t>Azure Hybrid Benefit</t>
+        </is>
+      </c>
+      <c r="B48" s="298" t="inlineStr">
+        <is>
+          <t>https://azure.microsoft.com/pricing/hybrid-benefit/</t>
+        </is>
+      </c>
+      <c r="C48" s="291" t="n"/>
+      <c r="D48" s="291" t="n"/>
+      <c r="E48" s="291" t="n"/>
+      <c r="F48" s="291" t="n"/>
+      <c r="G48" s="292" t="n"/>
+      <c r="H48" s="299" t="inlineStr">
+        <is>
+          <t>Calculate AHB savings for Windows Server and SQL Server licences</t>
+        </is>
+      </c>
+      <c r="I48" s="292" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="293" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="B49" s="298" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/ec2/pricing/reserved-instances/</t>
+        </is>
+      </c>
+      <c r="C49" s="291" t="n"/>
+      <c r="D49" s="291" t="n"/>
+      <c r="E49" s="291" t="n"/>
+      <c r="F49" s="291" t="n"/>
+      <c r="G49" s="292" t="n"/>
+      <c r="H49" s="299" t="inlineStr">
+        <is>
+          <t>AWS EC2 Reserved Instance pricing by region and commitment type</t>
+        </is>
+      </c>
+      <c r="I49" s="292" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="293" t="inlineStr">
+        <is>
+          <t>AWS Pricing Calculator</t>
+        </is>
+      </c>
+      <c r="B50" s="298" t="inlineStr">
+        <is>
+          <t>https://calculator.aws/pricing/2/home</t>
+        </is>
+      </c>
+      <c r="C50" s="291" t="n"/>
+      <c r="D50" s="291" t="n"/>
+      <c r="E50" s="291" t="n"/>
+      <c r="F50" s="291" t="n"/>
+      <c r="G50" s="292" t="n"/>
+      <c r="H50" s="299" t="inlineStr">
+        <is>
+          <t>Build configurable estimate; export for TCO model validation</t>
+        </is>
+      </c>
+      <c r="I50" s="292" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="293" t="inlineStr">
+        <is>
+          <t>GCP</t>
+        </is>
+      </c>
+      <c r="B51" s="298" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/compute/vm-instance-pricing</t>
+        </is>
+      </c>
+      <c r="C51" s="291" t="n"/>
+      <c r="D51" s="291" t="n"/>
+      <c r="E51" s="291" t="n"/>
+      <c r="F51" s="291" t="n"/>
+      <c r="G51" s="292" t="n"/>
+      <c r="H51" s="299" t="inlineStr">
+        <is>
+          <t>GCP Compute Engine pricing with CUD and SUD details</t>
+        </is>
+      </c>
+      <c r="I51" s="292" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="293" t="inlineStr">
+        <is>
+          <t>GCP Pricing Calculator</t>
+        </is>
+      </c>
+      <c r="B52" s="298" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/products/calculator</t>
+        </is>
+      </c>
+      <c r="C52" s="291" t="n"/>
+      <c r="D52" s="291" t="n"/>
+      <c r="E52" s="291" t="n"/>
+      <c r="F52" s="291" t="n"/>
+      <c r="G52" s="292" t="n"/>
+      <c r="H52" s="299" t="inlineStr">
+        <is>
+          <t>Build configurable estimate; compare 1yr vs 3yr CUD</t>
+        </is>
+      </c>
+      <c r="I52" s="292" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="293" t="inlineStr">
+        <is>
+          <t>Azure Migration &amp; Modernisation</t>
+        </is>
+      </c>
+      <c r="B53" s="298" t="inlineStr">
+        <is>
+          <t>https://azure.microsoft.com/solutions/migration/</t>
+        </is>
+      </c>
+      <c r="C53" s="291" t="n"/>
+      <c r="D53" s="291" t="n"/>
+      <c r="E53" s="291" t="n"/>
+      <c r="F53" s="291" t="n"/>
+      <c r="G53" s="292" t="n"/>
+      <c r="H53" s="299" t="inlineStr">
+        <is>
+          <t>AMM funding eligibility and deal registration portal</t>
+        </is>
+      </c>
+      <c r="I53" s="292" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="21">
+      <c r="A54" s="293" t="inlineStr">
+        <is>
+          <t>AWS MAP</t>
+        </is>
+      </c>
+      <c r="B54" s="298" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/migration-acceleration-program/</t>
+        </is>
+      </c>
+      <c r="C54" s="291" t="n"/>
+      <c r="D54" s="291" t="n"/>
+      <c r="E54" s="291" t="n"/>
+      <c r="F54" s="291" t="n"/>
+      <c r="G54" s="292" t="n"/>
+      <c r="H54" s="299" t="inlineStr">
+        <is>
+          <t>MAP funding eligibility and registration process</t>
+        </is>
+      </c>
+      <c r="I54" s="292" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C44:H44"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="C39:H39"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B48:G48"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2272,7 +4054,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -2457,7 +4238,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
@@ -2609,7 +4389,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="70" t="inlineStr">
         <is>
@@ -2681,7 +4460,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="47" t="inlineStr">
         <is>
@@ -2765,7 +4543,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="23" t="inlineStr">
         <is>
@@ -7888,7 +9665,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -7911,7 +9687,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="87" t="inlineStr">
         <is>
@@ -8102,7 +9877,6 @@
       </c>
       <c r="H16" s="81" t="n"/>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="89" t="inlineStr">
         <is>
@@ -8288,7 +10062,6 @@
       </c>
       <c r="H28" s="53" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="91" t="inlineStr">
         <is>
@@ -8474,7 +10247,6 @@
       </c>
       <c r="H40" s="58" t="n"/>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="62" t="inlineStr">
         <is>
@@ -8608,7 +10380,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" s="38" t="inlineStr">
         <is>
@@ -8643,7 +10414,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="96" t="inlineStr">
         <is>
@@ -8741,7 +10511,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="98" t="inlineStr">
         <is>
@@ -8841,7 +10610,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="A66" s="99" t="inlineStr">
         <is>
@@ -8939,7 +10707,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="73" t="inlineStr">
         <is>
@@ -9174,7 +10941,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="49" t="inlineStr">
         <is>
@@ -9189,7 +10955,6 @@
         </is>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="56" t="inlineStr">
         <is>
@@ -9361,7 +11126,6 @@
         </is>
       </c>
     </row>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="90" t="inlineStr">
         <is>
@@ -9526,7 +11290,6 @@
         </is>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="30" t="inlineStr">
         <is>
@@ -9691,7 +11454,6 @@
         </is>
       </c>
     </row>
-    <row r="115"/>
     <row r="116">
       <c r="A116" s="101" t="inlineStr">
         <is>
@@ -9834,7 +11596,6 @@
         </is>
       </c>
     </row>
-    <row r="123"/>
     <row r="124">
       <c r="A124" s="102" t="inlineStr">
         <is>
